--- a/_ForDRA/BVSimulationFiles/93.xlsx
+++ b/_ForDRA/BVSimulationFiles/93.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0005161290322580645</v>
+        <v>0.01032258064516129</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004927875137424688</v>
+        <v>0.009855750274849376</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004703530148957671</v>
+        <v>0.009407060297915342</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004488029974071644</v>
+        <v>0.008976059948143288</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004281142182187546</v>
+        <v>0.008562284364375092</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004082629043558053</v>
+        <v>0.008165258087116106</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003892249087370328</v>
+        <v>0.007784498174740656</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0003709758486544226</v>
+        <v>0.007419516973088453</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000353491228475562</v>
+        <v>0.007069824569511239</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0003367465479953218</v>
+        <v>0.006734930959906437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003207173977472737</v>
+        <v>0.006414347954945474</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003053795424777429</v>
+        <v>0.006107590849554858</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0002907089938862183</v>
+        <v>0.005814179877724366</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0002766820736443353</v>
+        <v>0.005533641472886706</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0002632754676212663</v>
+        <v>0.005265509352425326</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002504662721655446</v>
+        <v>0.005009325443310892</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0002382320332216291</v>
+        <v>0.004764640664432582</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002265507789934378</v>
+        <v>0.004531015579868756</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0002154010468061977</v>
+        <v>0.004308020936123954</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002047619047619047</v>
+        <v>0.004095238095238094</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0005161290322580645</v>
+        <v>0.01032258064516129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004927875137424688</v>
+        <v>0.009855750274849376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004703530148957671</v>
+        <v>0.009407060297915342</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004488029974071644</v>
+        <v>0.008976059948143288</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004281142182187546</v>
+        <v>0.008562284364375092</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004082629043558053</v>
+        <v>0.008165258087116106</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0003892249087370328</v>
+        <v>0.007784498174740656</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003709758486544226</v>
+        <v>0.007419516973088453</v>
       </c>
       <c r="J3" t="n">
-        <v>0.000353491228475562</v>
+        <v>0.007069824569511239</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003367465479953218</v>
+        <v>0.006734930959906437</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003207173977472737</v>
+        <v>0.006414347954945474</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0003053795424777429</v>
+        <v>0.006107590849554858</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0002907089938862183</v>
+        <v>0.005814179877724366</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0002766820736443353</v>
+        <v>0.005533641472886706</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0002632754676212663</v>
+        <v>0.005265509352425326</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002504662721655446</v>
+        <v>0.005009325443310892</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0002382320332216291</v>
+        <v>0.004764640664432582</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002265507789934378</v>
+        <v>0.004531015579868756</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0002154010468061977</v>
+        <v>0.004308020936123954</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002047619047619047</v>
+        <v>0.004095238095238094</v>
       </c>
     </row>
   </sheetData>
